--- a/tiflow-xborder/develop/2.0.0-ballot.2/CodeSystem-tiflow-xborder-operation-outcome-details-cs.xlsx
+++ b/tiflow-xborder/develop/2.0.0-ballot.2/CodeSystem-tiflow-xborder-operation-outcome-details-cs.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://gematik.de/fhir/erp-eu/CodeSystem/tiflow-xborder-operation-outcome-details-cs</t>
+    <t>https://gematik.de/fhir/tiflow-xborder/CodeSystem/tiflow-xborder-operation-outcome-details-cs</t>
   </si>
   <si>
     <t>Version</t>
